--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VICTOR_LARCO_HERRERA</t>
+          <t>VICTOR LARCO HERRERA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>211 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.130599999999999</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.0401</v>
-      </c>
-      <c r="I2" t="n">
-        <v>385</v>
-      </c>
-      <c r="J2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.1306</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.0401</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>224</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.14306</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.05513000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>132</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.14306</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.05513</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>1582</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.132379999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.0488</v>
-      </c>
-      <c r="I4" t="n">
-        <v>133</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.13238</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.0488</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1584 LA PROVIDENCIA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.140700000000002</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.05119999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>147</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.140700000000002</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.0512</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.14132</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.05865</v>
-      </c>
-      <c r="I6" t="n">
-        <v>501</v>
-      </c>
-      <c r="J6" t="n">
-        <v>26</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.14132</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.05865</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>80820 VICTOR LARCO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.14026</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.04967000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>908</v>
-      </c>
-      <c r="J7" t="n">
-        <v>47</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.14026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.04967</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>80891 AUGUSTO ALVA ASCURRA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.13242</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.04928</v>
-      </c>
-      <c r="I8" t="n">
-        <v>863</v>
-      </c>
-      <c r="J8" t="n">
-        <v>38</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.13242</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.04928</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>81017 SANTA EDELMIRA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.13503</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.0431</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1162</v>
-      </c>
-      <c r="J9" t="n">
-        <v>48</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.13503</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.0431</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>81025 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.14495</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.05086</v>
-      </c>
-      <c r="I10" t="n">
-        <v>999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.14495</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.05086</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>81026 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.138350000000003</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.04785</v>
-      </c>
-      <c r="I11" t="n">
-        <v>629</v>
-      </c>
-      <c r="J11" t="n">
-        <v>26</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.138350000000003</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.04785</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>LA INMACULADA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-8.132250000000003</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.03762</v>
-      </c>
-      <c r="I12" t="n">
-        <v>433</v>
-      </c>
-      <c r="J12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.132250000000003</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.03762</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>SAN JOSE OBRERO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.13148</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.04212</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1010</v>
-      </c>
-      <c r="J13" t="n">
-        <v>56</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-8.13148</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.04212</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-8.143420000000003</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.05547</v>
-      </c>
-      <c r="I14" t="n">
-        <v>90</v>
-      </c>
-      <c r="J14" t="n">
-        <v>8</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-8.143420000000003</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.05547</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>SAN JOSE OBRERO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-8.133089999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.04026</v>
-      </c>
-      <c r="I15" t="n">
-        <v>636</v>
-      </c>
-      <c r="J15" t="n">
-        <v>41</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-8.13309</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.04026</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>TERCER MILENIO</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-8.13429</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.04637</v>
-      </c>
-      <c r="I16" t="n">
-        <v>225</v>
-      </c>
-      <c r="J16" t="n">
-        <v>11</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-8.13429</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.04637</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>INTERAMERICANA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-8.131489999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.04058999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>407</v>
-      </c>
-      <c r="J17" t="n">
-        <v>25</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-8.13149</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.04059</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>PIO XII</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-8.1416</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.04507</v>
-      </c>
-      <c r="I18" t="n">
-        <v>962</v>
-      </c>
-      <c r="J18" t="n">
-        <v>39</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-8.1416</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.04507</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>SAN FRANCISCO DE ASIS SCHOOL</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-8.14241</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.05396</v>
-      </c>
-      <c r="I19" t="n">
-        <v>213</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-8.14241</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.05396</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>255384</t>
+          <t>855201</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>211 SANTISIMA NIÑA MARIA</t>
+          <t>SAN FRANCISCO DE ASIS SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.1306</t>
+          <t>-8.14241</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.0401</t>
+          <t>-79.05396</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>255398</t>
+          <t>255845</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>TERCER MILENIO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.14306</t>
+          <t>-8.13429</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.05513</t>
+          <t>-79.04637</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>255402</t>
+          <t>255384</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>211 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.13238</t>
+          <t>-8.1306</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.0488</t>
+          <t>-79.0401</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>385</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>255421</t>
+          <t>728369</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1584 LA PROVIDENCIA</t>
+          <t>INTERAMERICANA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.140700000000002</t>
+          <t>-8.13149</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.0512</t>
+          <t>-79.04059</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>407</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>255497</t>
+          <t>255534</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80820 VICTOR LARCO</t>
+          <t>81026 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.14026</t>
+          <t>-8.138350000000003</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.04967</t>
+          <t>-79.04785</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>629</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>255510</t>
+          <t>255553</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>81017 SANTA EDELMIRA</t>
+          <t>LA INMACULADA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.13503</t>
+          <t>-8.132250000000003</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.0431</t>
+          <t>-79.03762</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>255529</t>
+          <t>756140</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81025 JOSE ANTONIO ENCINAS</t>
+          <t>PIO XII</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.14495</t>
+          <t>-8.1416</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.05086</t>
+          <t>-79.04507</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>962</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>255534</t>
+          <t>255770</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>81026 ANDRES AVELINO CACERES</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.138350000000003</t>
+          <t>-8.13309</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.04785</t>
+          <t>-79.04026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>636</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>255553</t>
+          <t>255497</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LA INMACULADA</t>
+          <t>80820 VICTOR LARCO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.132250000000003</t>
+          <t>-8.14026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.03762</t>
+          <t>-79.04967</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>908</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>255708</t>
+          <t>255510</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>81017 SANTA EDELMIRA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.13148</t>
+          <t>-8.13503</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.04212</t>
+          <t>-79.0431</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>255765</t>
+          <t>255529</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>81025 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.143420000000003</t>
+          <t>-8.14495</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.05547</t>
+          <t>-79.05086</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>999</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>255770</t>
+          <t>255708</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.13309</t>
+          <t>-8.13148</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.04026</t>
+          <t>-79.04212</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>255845</t>
+          <t>255402</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TERCER MILENIO</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.13429</t>
+          <t>-8.13238</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.04637</t>
+          <t>-79.0488</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>728369</t>
+          <t>255421</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>INTERAMERICANA</t>
+          <t>1584 LA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.13149</t>
+          <t>-8.140700000000002</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.04059</t>
+          <t>-79.0512</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>756140</t>
+          <t>255765</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PIO XII</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.1416</t>
+          <t>-8.143420000000003</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.04507</t>
+          <t>-79.05547</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>855201</t>
+          <t>255398</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS SCHOOL</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.14241</t>
+          <t>-8.14306</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.05396</t>
+          <t>-79.05513</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.138350000000003</t>
+          <t>-8.13835</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.132250000000003</t>
+          <t>-8.13225</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.140700000000002</t>
+          <t>-8.1407</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.143420000000003</t>
+          <t>-8.14342</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
@@ -511,22 +511,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-8.14241</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-79.05396</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>255845</t>
+          <t>756140</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TERCER MILENIO</t>
+          <t>PIO XII</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.13429</t>
+          <t>962</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.04637</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-8.1416</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.04507</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>255384</t>
+          <t>728369</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>211 SANTISIMA NIÑA MARIA</t>
+          <t>INTERAMERICANA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.1306</t>
+          <t>407</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.0401</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>-8.13149</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.04059</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>728369</t>
+          <t>255845</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>INTERAMERICANA</t>
+          <t>TERCER MILENIO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.13149</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.04059</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>-8.13429</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-79.04637</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>255478</t>
+          <t>255770</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.14132</t>
+          <t>636</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.05865</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>-8.13309</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.04026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>255534</t>
+          <t>255765</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>81026 ANDRES AVELINO CACERES</t>
+          <t>NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.13835</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.04785</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>-8.143420000000003</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.05547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>255505</t>
+          <t>255708</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80891 AUGUSTO ALVA ASCURRA</t>
+          <t>SAN JOSE OBRERO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.13242</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.04928</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>-8.13148</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.04212</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -945,22 +945,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.13225</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-8.132250000000003</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>-79.03762</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>756140</t>
+          <t>255534</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PIO XII</t>
+          <t>81026 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.1416</t>
+          <t>629</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.04507</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>-8.138350000000003</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-79.04785</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>255770</t>
+          <t>255529</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>81025 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.13309</t>
+          <t>999</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.04026</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>-8.14495</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-79.05086</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>255497</t>
+          <t>255510</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80820 VICTOR LARCO</t>
+          <t>81017 SANTA EDELMIRA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.14026</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.04967</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>-8.13503</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-79.0431</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>255510</t>
+          <t>255505</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>81017 SANTA EDELMIRA</t>
+          <t>80891 AUGUSTO ALVA ASCURRA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.13503</t>
+          <t>863</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.0431</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>-8.13242</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-79.04928</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>255529</t>
+          <t>255497</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>81025 JOSE ANTONIO ENCINAS</t>
+          <t>80820 VICTOR LARCO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.14495</t>
+          <t>908</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.05086</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>-8.14026</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-79.04967</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>255708</t>
+          <t>255478</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN JOSE OBRERO</t>
+          <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.13148</t>
+          <t>501</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.04212</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>-8.14132</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-79.05865</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>255402</t>
+          <t>255421</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1584 LA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.13238</t>
+          <t>147</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.0488</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>-8.140700000000002</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-79.0512</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>255421</t>
+          <t>255402</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1584 LA PROVIDENCIA</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.1407</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.0512</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>-8.13238</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-79.0488</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>255765</t>
+          <t>255398</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CARMEN</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.14342</t>
+          <t>132</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.05547</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-8.14306</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.05513</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>255398</t>
+          <t>255384</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>211 SANTISIMA NIÑA MARIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.14306</t>
+          <t>385</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.05513</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-8.1306</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.0401</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-VICTOR_LARCO_HERRERA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
